--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_category_display.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_category_display.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C2" t="n">
-        <v>42.5</v>
+        <v>41.52</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>24.11</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>21.5</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>12.05</v>
       </c>
     </row>
   </sheetData>
